--- a/Result/profitability/6928.xlsx
+++ b/Result/profitability/6928.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM19"/>
+  <dimension ref="A1:AM20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2843,6 +2843,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6928</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>394</v>
+      </c>
+      <c r="D20" t="n">
+        <v>280</v>
+      </c>
+      <c r="E20" t="n">
+        <v>114</v>
+      </c>
+      <c r="F20" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-43</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-10.89%</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-34</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.215</v>
+      </c>
+      <c r="N20" t="n">
+        <v>25.92875</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="X20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.9300000000000033</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.03322615219721348</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.640000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.2422680412371134</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
